--- a/data/GreatLink/Singapore Physical Gold Fund.xlsx
+++ b/data/GreatLink/Singapore Physical Gold Fund.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="PriceHistory" sheetId="1" r:id="GemRid322720"/>
+    <sheet name="PriceHistory" sheetId="1" r:id="GemRid146092"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>Price Date</t>
   </si>
@@ -26,13 +26,100 @@
     <t>Currency - Unit Level</t>
   </si>
   <si>
+    <t>27/02/2026</t>
+  </si>
+  <si>
+    <t>0.941</t>
+  </si>
+  <si>
+    <t>SGD</t>
+  </si>
+  <si>
+    <t>26/02/2026</t>
+  </si>
+  <si>
+    <t>0.940</t>
+  </si>
+  <si>
+    <t>25/02/2026</t>
+  </si>
+  <si>
+    <t>24/02/2026</t>
+  </si>
+  <si>
+    <t>23/02/2026</t>
+  </si>
+  <si>
+    <t>0.937</t>
+  </si>
+  <si>
+    <t>20/02/2026</t>
+  </si>
+  <si>
+    <t>0.919</t>
+  </si>
+  <si>
+    <t>19/02/2026</t>
+  </si>
+  <si>
+    <t>0.911</t>
+  </si>
+  <si>
+    <t>16/02/2026</t>
+  </si>
+  <si>
+    <t>0.918</t>
+  </si>
+  <si>
+    <t>13/02/2026</t>
+  </si>
+  <si>
+    <t>12/02/2026</t>
+  </si>
+  <si>
+    <t>11/02/2026</t>
+  </si>
+  <si>
+    <t>0.920</t>
+  </si>
+  <si>
+    <t>10/02/2026</t>
+  </si>
+  <si>
+    <t>09/02/2026</t>
+  </si>
+  <si>
+    <t>0.913</t>
+  </si>
+  <si>
+    <t>06/02/2026</t>
+  </si>
+  <si>
+    <t>0.895</t>
+  </si>
+  <si>
+    <t>05/02/2026</t>
+  </si>
+  <si>
+    <t>0.894</t>
+  </si>
+  <si>
+    <t>04/02/2026</t>
+  </si>
+  <si>
+    <t>0.922</t>
+  </si>
+  <si>
+    <t>03/02/2026</t>
+  </si>
+  <si>
+    <t>0.905</t>
+  </si>
+  <si>
     <t>02/02/2026</t>
   </si>
   <si>
     <t>0.878</t>
-  </si>
-  <si>
-    <t>SGD</t>
   </si>
   <si>
     <t>30/01/2026</t>
@@ -429,7 +516,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -437,10 +524,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -448,10 +535,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -459,7 +546,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -470,12 +557,199 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
         <v>15</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" t="s">
         <v>5</v>
       </c>
     </row>

--- a/data/GreatLink/Singapore Physical Gold Fund.xlsx
+++ b/data/GreatLink/Singapore Physical Gold Fund.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="PriceHistory" sheetId="1" r:id="GemRid146092"/>
+    <sheet name="PriceHistory" sheetId="1" r:id="GemRid410516"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>Price Date</t>
   </si>
@@ -26,15 +26,165 @@
     <t>Currency - Unit Level</t>
   </si>
   <si>
+    <t>09/04/2026</t>
+  </si>
+  <si>
+    <t>0.871</t>
+  </si>
+  <si>
+    <t>SGD</t>
+  </si>
+  <si>
+    <t>08/04/2026</t>
+  </si>
+  <si>
+    <t>0.883</t>
+  </si>
+  <si>
+    <t>07/04/2026</t>
+  </si>
+  <si>
+    <t>0.868</t>
+  </si>
+  <si>
+    <t>06/04/2026</t>
+  </si>
+  <si>
+    <t>0.861</t>
+  </si>
+  <si>
+    <t>02/04/2026</t>
+  </si>
+  <si>
+    <t>01/04/2026</t>
+  </si>
+  <si>
+    <t>0.875</t>
+  </si>
+  <si>
+    <t>31/03/2026</t>
+  </si>
+  <si>
+    <t>0.850</t>
+  </si>
+  <si>
+    <t>30/03/2026</t>
+  </si>
+  <si>
+    <t>0.846</t>
+  </si>
+  <si>
+    <t>27/03/2026</t>
+  </si>
+  <si>
+    <t>0.826</t>
+  </si>
+  <si>
+    <t>26/03/2026</t>
+  </si>
+  <si>
+    <t>25/03/2026</t>
+  </si>
+  <si>
+    <t>0.845</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>0.819</t>
+  </si>
+  <si>
+    <t>23/03/2026</t>
+  </si>
+  <si>
+    <t>0.794</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>19/03/2026</t>
+  </si>
+  <si>
+    <t>18/03/2026</t>
+  </si>
+  <si>
+    <t>0.920</t>
+  </si>
+  <si>
+    <t>17/03/2026</t>
+  </si>
+  <si>
+    <t>0.925</t>
+  </si>
+  <si>
+    <t>16/03/2026</t>
+  </si>
+  <si>
+    <t>0.923</t>
+  </si>
+  <si>
+    <t>13/03/2026</t>
+  </si>
+  <si>
+    <t>0.941</t>
+  </si>
+  <si>
+    <t>12/03/2026</t>
+  </si>
+  <si>
+    <t>0.956</t>
+  </si>
+  <si>
+    <t>11/03/2026</t>
+  </si>
+  <si>
+    <t>0.955</t>
+  </si>
+  <si>
+    <t>10/03/2026</t>
+  </si>
+  <si>
+    <t>0.952</t>
+  </si>
+  <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
+    <t>0.944</t>
+  </si>
+  <si>
+    <t>06/03/2026</t>
+  </si>
+  <si>
+    <t>0.943</t>
+  </si>
+  <si>
+    <t>05/03/2026</t>
+  </si>
+  <si>
+    <t>0.951</t>
+  </si>
+  <si>
+    <t>04/03/2026</t>
+  </si>
+  <si>
+    <t>03/03/2026</t>
+  </si>
+  <si>
+    <t>0.970</t>
+  </si>
+  <si>
+    <t>02/03/2026</t>
+  </si>
+  <si>
+    <t>0.983</t>
+  </si>
+  <si>
     <t>27/02/2026</t>
   </si>
   <si>
-    <t>0.941</t>
-  </si>
-  <si>
-    <t>SGD</t>
-  </si>
-  <si>
     <t>26/02/2026</t>
   </si>
   <si>
@@ -78,9 +228,6 @@
   </si>
   <si>
     <t>11/02/2026</t>
-  </si>
-  <si>
-    <t>0.920</t>
   </si>
   <si>
     <t>10/02/2026</t>
@@ -516,7 +663,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -524,10 +671,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -535,7 +682,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -546,10 +693,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -557,10 +704,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -568,10 +715,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -579,10 +726,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -590,10 +737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -601,10 +748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -612,10 +759,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
         <v>5</v>
@@ -623,10 +770,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -634,10 +781,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -645,10 +792,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -656,10 +803,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
@@ -667,10 +814,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
         <v>5</v>
@@ -678,10 +825,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -689,10 +836,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -700,10 +847,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -711,10 +858,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
@@ -722,10 +869,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -733,10 +880,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
         <v>5</v>
@@ -744,12 +891,320 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>64</v>
+      </c>
+      <c r="B36" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>70</v>
+      </c>
+      <c r="B40" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>71</v>
+      </c>
+      <c r="B41" t="s">
+        <v>63</v>
+      </c>
+      <c r="C41" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>72</v>
+      </c>
+      <c r="B42" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>74</v>
+      </c>
+      <c r="B43" t="s">
+        <v>75</v>
+      </c>
+      <c r="C43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>76</v>
+      </c>
+      <c r="B44" t="s">
+        <v>77</v>
+      </c>
+      <c r="C44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>78</v>
+      </c>
+      <c r="B45" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>80</v>
+      </c>
+      <c r="B46" t="s">
+        <v>81</v>
+      </c>
+      <c r="C46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>82</v>
+      </c>
+      <c r="B47" t="s">
+        <v>83</v>
+      </c>
+      <c r="C47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>84</v>
+      </c>
+      <c r="B48" t="s">
+        <v>85</v>
+      </c>
+      <c r="C48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>86</v>
+      </c>
+      <c r="B49" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>88</v>
+      </c>
+      <c r="B50" t="s">
+        <v>89</v>
+      </c>
+      <c r="C50" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>90</v>
+      </c>
+      <c r="B51" t="s">
+        <v>91</v>
+      </c>
+      <c r="C51" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>92</v>
+      </c>
+      <c r="B52" t="s">
+        <v>91</v>
+      </c>
+      <c r="C52" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>93</v>
+      </c>
+      <c r="B53" t="s">
+        <v>94</v>
+      </c>
+      <c r="C53" t="s">
         <v>5</v>
       </c>
     </row>
